--- a/data/trans_camb/P16A02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A02-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 9,75</t>
+          <t>2,62; 9,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 9,14</t>
+          <t>1,39; 8,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,96; 20,13</t>
+          <t>11,17; 20,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 13,12</t>
+          <t>5,01; 12,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 13,71</t>
+          <t>5,19; 13,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,33; 31,79</t>
+          <t>24,1; 31,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 10,66</t>
+          <t>5,16; 10,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 10,87</t>
+          <t>4,75; 10,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,37; 26,18</t>
+          <t>20,09; 26,2</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,26; 57,6</t>
+          <t>12,32; 56,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 52,46</t>
+          <t>6,97; 52,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,18; 119,52</t>
+          <t>53,82; 117,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,23; 43,25</t>
+          <t>14,94; 41,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,57; 45,76</t>
+          <t>15,09; 45,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,84; 105,83</t>
+          <t>70,32; 105,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,13; 42,79</t>
+          <t>18,45; 42,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,99; 43,86</t>
+          <t>17,42; 42,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73,84; 104,6</t>
+          <t>73,28; 105,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,76</t>
+          <t>2,05; 6,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 7,75</t>
+          <t>3,06; 7,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 12,31</t>
+          <t>2,22; 12,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 13,91</t>
+          <t>7,97; 13,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 11,35</t>
+          <t>5,76; 11,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,5; 38,32</t>
+          <t>13,77; 36,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,5</t>
+          <t>5,4; 9,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,77</t>
+          <t>5,08; 8,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 26,13</t>
+          <t>9,82; 24,68</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,11; 63,57</t>
+          <t>16,46; 62,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,62; 72,05</t>
+          <t>23,66; 70,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,05; 111,6</t>
+          <t>20,4; 108,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,92; 81,62</t>
+          <t>39,31; 80,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,7; 66,36</t>
+          <t>27,68; 66,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,31; 211,63</t>
+          <t>71,37; 207,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,76; 66,41</t>
+          <t>33,42; 65,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,87; 61,5</t>
+          <t>31,67; 61,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65,38; 166,15</t>
+          <t>63,05; 168,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 3,15</t>
+          <t>-4,74; 3,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 10,9</t>
+          <t>2,6; 11,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 12,76</t>
+          <t>4,13; 13,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 13,61</t>
+          <t>1,52; 13,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 12,55</t>
+          <t>1,75; 12,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 15,07</t>
+          <t>6,2; 15,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 6,87</t>
+          <t>0,02; 7,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,71</t>
+          <t>4,02; 10,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,61; 13,36</t>
+          <t>6,46; 12,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-36,92; 31,62</t>
+          <t>-35,53; 34,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,12; 111,06</t>
+          <t>18,49; 118,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,56; 121,82</t>
+          <t>29,4; 135,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,81; 81,26</t>
+          <t>6,06; 78,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,34; 75,24</t>
+          <t>7,09; 74,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,22; 91,76</t>
+          <t>27,64; 98,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 49,21</t>
+          <t>-0,19; 50,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,92; 77,84</t>
+          <t>24,36; 78,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39,61; 99,11</t>
+          <t>38,38; 94,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,78</t>
+          <t>2,18; 5,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,85</t>
+          <t>2,98; 6,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,92; 11,2</t>
+          <t>3,36; 11,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,42; 11,73</t>
+          <t>7,43; 11,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,34</t>
+          <t>5,09; 9,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,77; 30,65</t>
+          <t>13,69; 28,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,14</t>
+          <t>5,44; 8,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,58</t>
+          <t>4,72; 7,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,9; 19,69</t>
+          <t>9,93; 19,65</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,69; 44,19</t>
+          <t>14,87; 44,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,59; 52,6</t>
+          <t>20,33; 50,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28,11; 84,68</t>
+          <t>22,78; 84,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29,84; 51,19</t>
+          <t>30,15; 52,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,87; 40,46</t>
+          <t>20,3; 41,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,65; 127,31</t>
+          <t>56,06; 123,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,46; 44,74</t>
+          <t>27,95; 45,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,73; 41,17</t>
+          <t>23,79; 40,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51,35; 104,06</t>
+          <t>51,31; 105,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A02-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,72</t>
+          <t>14,43</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,78</t>
+          <t>27,03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23,33</t>
+          <t>22,17</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,67</t>
+          <t>2,43; 9,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,95</t>
+          <t>1,5; 9,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,17; 20,07</t>
+          <t>9,84; 18,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 12,72</t>
+          <t>4,97; 12,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 13,9</t>
+          <t>5,27; 14,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,1; 31,35</t>
+          <t>23,47; 30,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,79</t>
+          <t>4,93; 10,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 10,7</t>
+          <t>5,01; 10,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,09; 26,2</t>
+          <t>19,1; 25,07</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,32; 56,1</t>
+          <t>12,31; 58,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 52,29</t>
+          <t>7,51; 54,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,82; 117,81</t>
+          <t>47,4; 107,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 41,87</t>
+          <t>15,15; 41,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,09; 45,66</t>
+          <t>15,33; 45,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,32; 105,83</t>
+          <t>68,4; 102,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,45; 42,86</t>
+          <t>18,01; 41,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,42; 42,95</t>
+          <t>17,89; 43,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73,28; 105,58</t>
+          <t>69,49; 101,22</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,73</t>
+          <t>10,85</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,98</t>
+          <t>16,03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,85</t>
+          <t>13,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,72</t>
+          <t>1,94; 6,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,61</t>
+          <t>2,91; 7,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 12,19</t>
+          <t>8,12; 13,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 13,75</t>
+          <t>8,26; 13,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 11,5</t>
+          <t>5,94; 11,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,77; 36,69</t>
+          <t>13,4; 18,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,32</t>
+          <t>5,62; 9,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,73</t>
+          <t>5,07; 8,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,82; 24,68</t>
+          <t>11,62; 15,3</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>112,99%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,46; 62,84</t>
+          <t>14,4; 63,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,66; 70,41</t>
+          <t>21,36; 72,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,4; 108,84</t>
+          <t>62,24; 125,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39,31; 80,52</t>
+          <t>41,23; 79,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,68; 66,46</t>
+          <t>28,92; 66,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,37; 207,46</t>
+          <t>66,54; 109,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,42; 65,18</t>
+          <t>35,27; 64,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,67; 61,71</t>
+          <t>31,57; 61,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63,05; 168,46</t>
+          <t>71,77; 108,16</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,27</t>
+          <t>8,28</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,67</t>
+          <t>10,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,8</t>
+          <t>9,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 3,25</t>
+          <t>-4,6; 3,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 11,18</t>
+          <t>2,3; 10,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 13,17</t>
+          <t>4,01; 12,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,12</t>
+          <t>2,31; 14,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 12,22</t>
+          <t>1,95; 12,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 15,61</t>
+          <t>5,43; 14,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,0</t>
+          <t>-0,03; 6,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 10,82</t>
+          <t>3,98; 10,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 12,77</t>
+          <t>6,45; 12,59</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>63,73%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 34,73</t>
+          <t>-34,94; 35,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,49; 118,37</t>
+          <t>16,94; 110,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,4; 135,82</t>
+          <t>29,58; 136,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,06; 78,11</t>
+          <t>11,49; 88,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,09; 74,5</t>
+          <t>9,11; 76,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,64; 98,13</t>
+          <t>24,68; 89,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 50,93</t>
+          <t>0,25; 51,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,36; 78,84</t>
+          <t>23,18; 78,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,38; 94,11</t>
+          <t>38,31; 94,47</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,55</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,08</t>
+          <t>15,08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,51</t>
+          <t>12,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,85</t>
+          <t>2,26; 5,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,68</t>
+          <t>3,14; 6,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,36; 11,22</t>
+          <t>8,05; 11,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,43; 11,85</t>
+          <t>7,28; 11,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,4</t>
+          <t>5,03; 9,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,69; 28,42</t>
+          <t>13,12; 17,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,44; 8,28</t>
+          <t>5,47; 8,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,53</t>
+          <t>4,58; 7,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,93; 19,65</t>
+          <t>11,26; 14,08</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,87; 44,62</t>
+          <t>15,27; 44,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,33; 50,81</t>
+          <t>21,48; 52,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,78; 84,59</t>
+          <t>54,75; 91,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,15; 52,41</t>
+          <t>29,25; 52,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,3; 41,83</t>
+          <t>20,16; 41,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,06; 123,13</t>
+          <t>52,32; 76,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,95; 45,48</t>
+          <t>27,65; 45,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,79; 40,66</t>
+          <t>23,28; 40,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51,31; 105,3</t>
+          <t>57,2; 77,2</t>
         </is>
       </c>
     </row>
